--- a/docs/reports/out/SWP490_FA26SE260_R2_ProjectTracking.xlsx
+++ b/docs/reports/out/SWP490_FA26SE260_R2_ProjectTracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\Project\CampusStay FPT\docs\reports\out\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{65201DB7-E104-4A39-967C-0CABF525C47A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD214528-B374-40F6-A03B-2B8B8B54989F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WBS" sheetId="8" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="317">
   <si>
     <t>Notes</t>
   </si>
@@ -580,12 +580,18 @@
     <t>FR-MOB-01 (Report 3 §3.12.1)</t>
   </si>
   <si>
+    <t>API documentation: Swagger UI and the OpenAPI document; Postman collection by role with smoke tests</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>springdoc-openapi; postman/ (288 requests, 49 smoke tests); docs/tools/generate-postman.mjs</t>
+  </si>
+  <si>
     <t>End-to-end workflow tests WF-01..05 on staging</t>
   </si>
   <si>
-    <t>Testing</t>
-  </si>
-  <si>
     <t>TC-WF-01..05, demo scenarios DS-01..10</t>
   </si>
   <si>
@@ -607,7 +613,10 @@
     <t>TC-NFR-03 (gap G4)</t>
   </si>
   <si>
-    <t>Android UI tests (sign-in, payment claim, door code)</t>
+    <t>Mobile app UI tests (sign-in, payment claim, door code)</t>
+  </si>
+  <si>
+    <t>Mobile app (Flutter)</t>
   </si>
   <si>
     <t>Gap G5</t>
@@ -884,6 +893,51 @@
   </si>
   <si>
     <t>docs 28/10/2026</t>
+  </si>
+  <si>
+    <t>Student Home crashed after a Deposit claim while nothing was due and no Bed was given</t>
+  </si>
+  <si>
+    <t>fix 28/10/2026 (commit 4138397)</t>
+  </si>
+  <si>
+    <t>Manager › Student hub</t>
+  </si>
+  <si>
+    <t>The Student hub crashed for a student with a Room (unknown table size)</t>
+  </si>
+  <si>
+    <t>Room map</t>
+  </si>
+  <si>
+    <t>The room map showed thin lines instead of bed squares</t>
+  </si>
+  <si>
+    <t>Student list and reconciliation templates</t>
+  </si>
+  <si>
+    <t>Excel set to Vietnamese opened the comma CSV template as one column</t>
+  </si>
+  <si>
+    <t>fix 28/10/2026: XLSX templates (commit 4138397)</t>
+  </si>
+  <si>
+    <t>Web screen map</t>
+  </si>
+  <si>
+    <t>The screen map generator found only the public pages after the router loaded pages on first visit</t>
+  </si>
+  <si>
+    <t>docs 30/10/2026: generator reads lazy page imports</t>
+  </si>
+  <si>
+    <t>Report 2</t>
+  </si>
+  <si>
+    <t>Report 2 PDF still named Kotlin and Jetpack Compose after the mobile app moved to Flutter</t>
+  </si>
+  <si>
+    <t>Rebuild Report 2 from its source (Flutter since 28/10/2026)</t>
   </si>
   <si>
     <t>How can a dormitory that does not operate yet be specified?</t>
@@ -1448,7 +1502,7 @@
   <sheetPr>
     <outlinePr summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr defaultColWidth="10.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.77734375" style="8" customWidth="1"/>
@@ -3069,7 +3123,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" ht="105.6" x14ac:dyDescent="0.25">
       <c r="A76" s="13">
         <v>69</v>
       </c>
@@ -3080,19 +3134,19 @@
         <v>181</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="E76" s="14" t="s">
         <v>182</v>
       </c>
       <c r="F76" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G76" s="15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="31.2" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A77" s="13">
         <v>70</v>
       </c>
@@ -3115,7 +3169,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A78" s="13">
         <v>71</v>
       </c>
@@ -3126,7 +3180,7 @@
         <v>181</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="E78" s="14" t="s">
         <v>186</v>
@@ -3138,7 +3192,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A79" s="13">
         <v>72</v>
       </c>
@@ -3169,7 +3223,7 @@
         <v>189</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D80" s="14" t="s">
         <v>3</v>
@@ -3184,7 +3238,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A81" s="13">
         <v>74</v>
       </c>
@@ -3224,21 +3278,21 @@
         <v>196</v>
       </c>
       <c r="F82" s="15" t="s">
-        <v>197</v>
+        <v>28</v>
       </c>
       <c r="G82" s="15" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A83" s="13">
         <v>76</v>
       </c>
       <c r="B83" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="C83" s="14" t="s">
         <v>198</v>
-      </c>
-      <c r="C83" s="14" t="s">
-        <v>195</v>
       </c>
       <c r="D83" s="14" t="s">
         <v>3</v>
@@ -3247,9 +3301,32 @@
         <v>199</v>
       </c>
       <c r="F83" s="15" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G83" s="15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A84" s="13">
+        <v>77</v>
+      </c>
+      <c r="B84" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="C84" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="D84" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E84" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="F84" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="G84" s="15" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3327,28 +3404,28 @@
         <v>1</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="I4" s="19" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3356,28 +3433,28 @@
         <v>2</v>
       </c>
       <c r="B5" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="G5" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="H5" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="D5" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>204</v>
-      </c>
-      <c r="G5" s="19" t="s">
-        <v>205</v>
-      </c>
-      <c r="H5" s="18" t="s">
-        <v>206</v>
-      </c>
       <c r="I5" s="19" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3385,28 +3462,28 @@
         <v>3</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="I6" s="19" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3414,28 +3491,28 @@
         <v>4</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="I7" s="19" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3443,28 +3520,28 @@
         <v>5</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="I8" s="19" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3472,26 +3549,26 @@
         <v>6</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G9" s="19"/>
       <c r="H9" s="18" t="s">
         <v>20</v>
       </c>
       <c r="I9" s="19" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3499,26 +3576,26 @@
         <v>7</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D10" s="18" t="s">
         <v>3</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G10" s="19"/>
       <c r="H10" s="18" t="s">
         <v>20</v>
       </c>
       <c r="I10" s="19" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3526,26 +3603,26 @@
         <v>8</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C11" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="F11" s="19" t="s">
         <v>232</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>229</v>
       </c>
       <c r="G11" s="19"/>
       <c r="H11" s="18" t="s">
         <v>20</v>
       </c>
       <c r="I11" s="19" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3553,26 +3630,26 @@
         <v>9</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D12" s="18" t="s">
         <v>3</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="G12" s="19"/>
       <c r="H12" s="18" t="s">
         <v>20</v>
       </c>
       <c r="I12" s="19" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -3595,7 +3672,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17.44140625" customWidth="1"/>
@@ -3636,22 +3713,22 @@
         <v>169</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
@@ -3659,275 +3736,413 @@
         <v>169</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G10" s="20" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G12" s="20" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="20" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F16" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>266</v>
+      </c>
+      <c r="C17" s="20" t="s">
         <v>206</v>
       </c>
-      <c r="G16" s="20" t="s">
-        <v>281</v>
+      <c r="D17" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>289</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>290</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>292</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>295</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -3977,93 +4192,93 @@
     </row>
     <row r="4" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="A4" s="21" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E4" s="22" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="A5" s="21" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="A6" s="21" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="A7" s="21" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="A8" s="21" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="D8" s="22" t="s">
         <v>3</v>
@@ -4072,18 +4287,18 @@
         <v>20</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="A9" s="21" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="D9" s="22" t="s">
         <v>3</v>
@@ -4092,18 +4307,18 @@
         <v>20</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A10" s="21" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="D10" s="22" t="s">
         <v>3</v>

--- a/docs/reports/out/SWP490_FA26SE260_R2_ProjectTracking.xlsx
+++ b/docs/reports/out/SWP490_FA26SE260_R2_ProjectTracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\Project\CampusStay FPT\docs\reports\out\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD214528-B374-40F6-A03B-2B8B8B54989F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{49A8EDF8-F649-49D1-A716-B8EEDD9BAF4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="322">
   <si>
     <t>Notes</t>
   </si>
@@ -920,6 +920,21 @@
   </si>
   <si>
     <t>fix 28/10/2026: XLSX templates (commit 4138397)</t>
+  </si>
+  <si>
+    <t>Manager and Admin dashboards</t>
+  </si>
+  <si>
+    <t>Money collected differed between the dashboards and Collections and refunds (Deposits without a Bed left out); a rate with debt left could read 100 %</t>
+  </si>
+  <si>
+    <t>fix 30/10/2026 (A-63); TC-RPT-015</t>
+  </si>
+  <si>
+    <t>Admin dashboard</t>
+  </si>
+  <si>
+    <t>Residents counted only desk check-ins, not released door codes (ADR-23)</t>
   </si>
   <si>
     <t>Web screen map</t>
@@ -3672,7 +3687,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17.44140625" customWidth="1"/>
@@ -4101,7 +4116,7 @@
     </row>
     <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="20" t="s">
-        <v>198</v>
+        <v>169</v>
       </c>
       <c r="B21" s="20" t="s">
         <v>294</v>
@@ -4124,7 +4139,7 @@
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
-        <v>198</v>
+        <v>169</v>
       </c>
       <c r="B22" s="20" t="s">
         <v>297</v>
@@ -4136,13 +4151,59 @@
         <v>298</v>
       </c>
       <c r="E22" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="E24" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="F22" s="20" t="s">
+      <c r="F24" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="20" t="s">
-        <v>299</v>
+      <c r="G24" s="20" t="s">
+        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -4195,10 +4256,10 @@
         <v>207</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="D4" s="22" t="s">
         <v>205</v>
@@ -4207,7 +4268,7 @@
         <v>209</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="27" x14ac:dyDescent="0.3">
@@ -4215,10 +4276,10 @@
         <v>207</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="D5" s="22" t="s">
         <v>205</v>
@@ -4227,7 +4288,7 @@
         <v>209</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="27" x14ac:dyDescent="0.3">
@@ -4235,10 +4296,10 @@
         <v>223</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="D6" s="22" t="s">
         <v>205</v>
@@ -4247,7 +4308,7 @@
         <v>209</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="27" x14ac:dyDescent="0.3">
@@ -4255,10 +4316,10 @@
         <v>219</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="D7" s="22" t="s">
         <v>205</v>
@@ -4267,7 +4328,7 @@
         <v>209</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="27" x14ac:dyDescent="0.3">
@@ -4275,10 +4336,10 @@
         <v>232</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D8" s="22" t="s">
         <v>3</v>
@@ -4287,7 +4348,7 @@
         <v>20</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="27" x14ac:dyDescent="0.3">
@@ -4295,10 +4356,10 @@
         <v>232</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D9" s="22" t="s">
         <v>3</v>
@@ -4307,7 +4368,7 @@
         <v>20</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="40.200000000000003" x14ac:dyDescent="0.3">
@@ -4315,10 +4376,10 @@
         <v>232</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="D10" s="22" t="s">
         <v>3</v>
